--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="745321229"/>
-        <c:axId val="2114748053"/>
+        <c:axId val="274599471"/>
+        <c:axId val="1368617330"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="745321229"/>
+        <c:axId val="274599471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2114748053"/>
+        <c:crossAx val="1368617330"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2114748053"/>
+        <c:axId val="1368617330"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="745321229"/>
+        <c:crossAx val="274599471"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1079,7 +1079,7 @@
     <xdr:ext cx="1219200" cy="2105025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image2.jpg"/>
+        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1107,7 +1107,7 @@
     <xdr:ext cx="1447800" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="274599471"/>
-        <c:axId val="1368617330"/>
+        <c:axId val="1651086956"/>
+        <c:axId val="143231248"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="274599471"/>
+        <c:axId val="1651086956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1368617330"/>
+        <c:crossAx val="143231248"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1368617330"/>
+        <c:axId val="143231248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="274599471"/>
+        <c:crossAx val="1651086956"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1651086956"/>
-        <c:axId val="143231248"/>
+        <c:axId val="690821892"/>
+        <c:axId val="713202657"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="1651086956"/>
+        <c:axId val="690821892"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143231248"/>
+        <c:crossAx val="713202657"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="143231248"/>
+        <c:axId val="713202657"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1651086956"/>
+        <c:crossAx val="690821892"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="690821892"/>
-        <c:axId val="713202657"/>
+        <c:axId val="130964249"/>
+        <c:axId val="972351612"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="690821892"/>
+        <c:axId val="130964249"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="713202657"/>
+        <c:crossAx val="972351612"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="713202657"/>
+        <c:axId val="972351612"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="690821892"/>
+        <c:crossAx val="130964249"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="130964249"/>
-        <c:axId val="972351612"/>
+        <c:axId val="673415661"/>
+        <c:axId val="858615613"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="130964249"/>
+        <c:axId val="673415661"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="972351612"/>
+        <c:crossAx val="858615613"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="972351612"/>
+        <c:axId val="858615613"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="130964249"/>
+        <c:crossAx val="673415661"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1079,7 +1079,7 @@
     <xdr:ext cx="1219200" cy="2105025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image1.jpg"/>
+        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1107,7 +1107,7 @@
     <xdr:ext cx="1447800" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="673415661"/>
-        <c:axId val="858615613"/>
+        <c:axId val="127084918"/>
+        <c:axId val="175392270"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="673415661"/>
+        <c:axId val="127084918"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="858615613"/>
+        <c:crossAx val="175392270"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="858615613"/>
+        <c:axId val="175392270"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="673415661"/>
+        <c:crossAx val="127084918"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="127084918"/>
-        <c:axId val="175392270"/>
+        <c:axId val="1771886086"/>
+        <c:axId val="136376151"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="127084918"/>
+        <c:axId val="1771886086"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="175392270"/>
+        <c:crossAx val="136376151"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="175392270"/>
+        <c:axId val="136376151"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="127084918"/>
+        <c:crossAx val="1771886086"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1079,7 +1079,7 @@
     <xdr:ext cx="1219200" cy="2105025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image2.jpg"/>
+        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1107,7 +1107,7 @@
     <xdr:ext cx="1447800" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1771886086"/>
-        <c:axId val="136376151"/>
+        <c:axId val="1701598425"/>
+        <c:axId val="1513114863"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="1771886086"/>
+        <c:axId val="1701598425"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="136376151"/>
+        <c:crossAx val="1513114863"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="136376151"/>
+        <c:axId val="1513114863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1771886086"/>
+        <c:crossAx val="1701598425"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1079,7 +1079,7 @@
     <xdr:ext cx="1219200" cy="2105025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image1.jpg"/>
+        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1107,7 +1107,7 @@
     <xdr:ext cx="1447800" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1701598425"/>
-        <c:axId val="1513114863"/>
+        <c:axId val="131291237"/>
+        <c:axId val="609254064"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="1701598425"/>
+        <c:axId val="131291237"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1513114863"/>
+        <c:crossAx val="609254064"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1513114863"/>
+        <c:axId val="609254064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1701598425"/>
+        <c:crossAx val="131291237"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="131291237"/>
-        <c:axId val="609254064"/>
+        <c:axId val="1666020971"/>
+        <c:axId val="738736320"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="131291237"/>
+        <c:axId val="1666020971"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="609254064"/>
+        <c:crossAx val="738736320"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="609254064"/>
+        <c:axId val="738736320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="131291237"/>
+        <c:crossAx val="1666020971"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1079,7 +1079,7 @@
     <xdr:ext cx="1219200" cy="2105025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image2.jpg"/>
+        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1107,7 +1107,7 @@
     <xdr:ext cx="1447800" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1666020971"/>
-        <c:axId val="738736320"/>
+        <c:axId val="830831026"/>
+        <c:axId val="1162326935"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="1666020971"/>
+        <c:axId val="830831026"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="738736320"/>
+        <c:crossAx val="1162326935"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="738736320"/>
+        <c:axId val="1162326935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1666020971"/>
+        <c:crossAx val="830831026"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1079,7 +1079,7 @@
     <xdr:ext cx="1219200" cy="2105025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image1.jpg"/>
+        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1107,7 +1107,7 @@
     <xdr:ext cx="1447800" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="830831026"/>
-        <c:axId val="1162326935"/>
+        <c:axId val="145929414"/>
+        <c:axId val="509381163"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="830831026"/>
+        <c:axId val="145929414"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1162326935"/>
+        <c:crossAx val="509381163"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1162326935"/>
+        <c:axId val="509381163"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="830831026"/>
+        <c:crossAx val="145929414"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1079,7 +1079,7 @@
     <xdr:ext cx="1219200" cy="2105025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image2.jpg"/>
+        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1107,7 +1107,7 @@
     <xdr:ext cx="1447800" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="145929414"/>
-        <c:axId val="509381163"/>
+        <c:axId val="1470221111"/>
+        <c:axId val="838087563"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="145929414"/>
+        <c:axId val="1470221111"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="509381163"/>
+        <c:crossAx val="838087563"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="509381163"/>
+        <c:axId val="838087563"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="145929414"/>
+        <c:crossAx val="1470221111"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1470221111"/>
-        <c:axId val="838087563"/>
+        <c:axId val="868635565"/>
+        <c:axId val="2027031939"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="1470221111"/>
+        <c:axId val="868635565"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="838087563"/>
+        <c:crossAx val="2027031939"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="838087563"/>
+        <c:axId val="2027031939"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1470221111"/>
+        <c:crossAx val="868635565"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>

--- a/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Riesgos Fase Construcción, Iteración 1 - Anexo I - Kairos - NexTech.xlsx
@@ -3,10 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Portada" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Identificación y Evaluación" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Resumen" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Análisis" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Portada" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Identificación y Evaluación" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Resumen" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Análisis" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">'Análisis'!$C$1:$C$480</definedName>
@@ -693,11 +693,11 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="868635565"/>
-        <c:axId val="2027031939"/>
+        <c:axId val="659427238"/>
+        <c:axId val="1241493103"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="868635565"/>
+        <c:axId val="659427238"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -749,10 +749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2027031939"/>
+        <c:crossAx val="1241493103"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2027031939"/>
+        <c:axId val="1241493103"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -827,7 +827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="868635565"/>
+        <c:crossAx val="659427238"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1079,7 +1079,7 @@
     <xdr:ext cx="1219200" cy="2105025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image1.jpg"/>
+        <xdr:cNvPr descr="UNPA.JPG" id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1107,7 +1107,7 @@
     <xdr:ext cx="1447800" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1164,6 +1164,10 @@
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
